--- a/assets/metrics/ikuma_89day_summary.xlsx
+++ b/assets/metrics/ikuma_89day_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9210442\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/itourikuto/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0013F552-89E4-4A76-A8FB-E06EA55B3121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3686EE8F-C945-6445-958E-3D0D547DF457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7215" yWindow="2595" windowWidth="21600" windowHeight="11295" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要サマリー" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="853">
   <si>
     <t>イクマ Instagram 89日間 集計サマリー</t>
   </si>
@@ -2373,254 +2373,569 @@
     <t>131</t>
   </si>
   <si>
-    <t>日付</t>
+    <t>日次</t>
     <rPh sb="0" eb="2">
-      <t>ヒヅケ</t>
+      <t>ニティ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>閲覧数</t>
-    <rPh sb="0" eb="3">
-      <t>エツランスウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>閲覧者数</t>
-    <rPh sb="0" eb="4">
-      <t>エツランシャスウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>平均再生時間</t>
-    <rPh sb="0" eb="6">
-      <t>ヘイキンサイセイジカン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>フォロー数</t>
-    <rPh sb="4" eb="5">
-      <t>スウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>スキップ率</t>
-    <rPh sb="4" eb="5">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>シェア率</t>
-    <rPh sb="3" eb="4">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>いいね率</t>
-    <rPh sb="3" eb="4">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>保存率</t>
-    <rPh sb="0" eb="3">
-      <t>ホゾンリツ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>再投稿率</t>
-    <rPh sb="0" eb="3">
-      <t>サイトウコウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>コメント率</t>
-    <rPh sb="4" eb="5">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
       <t>ガイヨウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>閲覧数に影響するもの</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>閲覧数</t>
     <rPh sb="0" eb="3">
-      <t>エツランスウ</t>
+      <t>エツランス</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>エイキョウ</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>閲覧者数</t>
+    <rPh sb="0" eb="3">
+      <t>エツラn</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>閲覧数の上位ソース</t>
+    <rPh sb="3" eb="4">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>平均再生時間</t>
+    <rPh sb="0" eb="6">
+      <t>ヘイキn</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>フォロー数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>スキップ率</t>
+    <rPh sb="4" eb="5">
+      <t>リテゥ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>シャア率</t>
+    <rPh sb="3" eb="4">
+      <t>リテゥ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>いいね率</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>保存率</t>
     <rPh sb="0" eb="3">
-      <t>エツランスウ</t>
+      <t>ホゾn</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウイ</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>再投稿率</t>
+    <rPh sb="0" eb="4">
+      <t>サイトウコウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>コメント率</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>閲覧の上位ソース</t>
+    <rPh sb="0" eb="2">
+      <t>エツラn</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>［リール］タブ</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>フィード</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>発見</t>
     <rPh sb="0" eb="2">
-      <t>ハッケン</t>
+      <t>ハッケn</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>プロフィール</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>エンゲージメント</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>プロフィールアクセス数</t>
-    <rPh sb="10" eb="11">
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>プロフのアクセス数</t>
+    <rPh sb="8" eb="9">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>プロフのリンクタップ数</t>
-    <rPh sb="10" eb="11">
-      <t>スウ</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>自己紹介のリンククリック</t>
+    <rPh sb="0" eb="4">
+      <t>ジコショウカイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>いいね数</t>
     <rPh sb="3" eb="4">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>コメント数</t>
     <rPh sb="4" eb="5">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>再投稿数</t>
-    <rPh sb="0" eb="4">
-      <t>サイトウコウスウ</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>再投稿</t>
+    <rPh sb="0" eb="3">
+      <t>サイトウコウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>シェア数</t>
-    <rPh sb="3" eb="4">
-      <t>スウ</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>保存数</t>
+    <rPh sb="0" eb="3">
+      <t>ホゾn</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>保存数</t>
-    <rPh sb="0" eb="2">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>スウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>オーディエンス</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>フォロワー</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>フォロワー以外</t>
     <rPh sb="5" eb="7">
       <t>イガイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>13-17</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>13−17</t>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>18-24</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>25-34</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>35-44</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>45-54</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>55-64</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>65＋</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>65+</t>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>男性</t>
     <rPh sb="0" eb="2">
       <t>ダンセイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>女性</t>
     <rPh sb="0" eb="2">
       <t>ジョセイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>動画尺</t>
+    <rPh sb="0" eb="3">
+      <t>ドウガ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>二頭筋を爆発的にデカくする〜４選〜</t>
+    <rPh sb="0" eb="3">
+      <t>ニトウク</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>バクハテゥ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t xml:space="preserve">セン </t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>二頭で妊娠するためにやること</t>
+    <rPh sb="0" eb="1">
+      <t>ニトウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニンシn</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋肉が大きくなる仕組み</t>
+    <rPh sb="0" eb="2">
+      <t>キンニク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オオキク</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>腹筋100回やっても腹筋は割れない</t>
+    <rPh sb="0" eb="2">
+      <t>フッキn</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ワレ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>ストーリーズ</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>ー</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>細かい筋トレよりもまずはBIG３を鍛えろ</t>
+    <rPh sb="0" eb="1">
+      <t>コマカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キントレ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>キタエ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>13..3%</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>20歳前後で筋トレしてない人へ</t>
+    <rPh sb="2" eb="3">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゼンゴデ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キントレ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>００バランスを整える知識</t>
+    <rPh sb="7" eb="8">
+      <t>トトノエ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チシキ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>胸トレルーティン</t>
+    <rPh sb="0" eb="1">
+      <t>ムネ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋肉の嘘・本当</t>
+    <rPh sb="0" eb="1">
+      <t>キンニク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ウソ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ホn</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>検索</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋肉×有酸素</t>
+    <rPh sb="0" eb="2">
+      <t>KINNNIK</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>YUUSANNS</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>マルチビタミン×筋肥大</t>
+    <rPh sb="8" eb="11">
+      <t>キn</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>タンパク質×筋合成</t>
+    <rPh sb="6" eb="9">
+      <t>キn</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>シェイカー紹介</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋トレしてるなら常識</t>
+    <rPh sb="0" eb="1">
+      <t>キントレ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>まだ10回3セットに縛られてない？</t>
+    <rPh sb="10" eb="11">
+      <t>シバラレ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>29,6%</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋肥大は「頑張る」より「理解」</t>
+    <rPh sb="0" eb="1">
+      <t>キンヒダイヘ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガンバル</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>リカイ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>8.8.%</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>飲みすぎた次の日にやっていること</t>
+    <rPh sb="0" eb="1">
+      <t>ノミスギ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>大胸筋で黙らせろ</t>
+    <rPh sb="0" eb="3">
+      <t>ダイキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ダマラ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋トレ後にやった方がいいこと〜５選〜</t>
+    <rPh sb="0" eb="1">
+      <t>キントレ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ゴニ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋肉がデカくなる本当の仕組み</t>
+    <rPh sb="0" eb="1">
+      <t>キンニク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホn</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>7.7.%</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋肥大させたいなら水も大事</t>
+    <rPh sb="0" eb="1">
+      <t>キンヒダ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ダイジ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>今日ジムに入会した21歳</t>
+    <rPh sb="0" eb="2">
+      <t>キョウジム</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウカイ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>1時間で終わる背中トレメニュー</t>
+    <rPh sb="7" eb="9">
+      <t>セナカ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋トレ×サウナ</t>
+    <rPh sb="0" eb="1">
+      <t>キントレ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋トレ×睡眠</t>
+    <rPh sb="0" eb="1">
+      <t>🏋️カケル</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>スイミn</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋トレ初心者が知るべき数字</t>
+    <rPh sb="3" eb="6">
+      <t>ショシn</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シル</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋トレ×タバコの現実</t>
+    <rPh sb="3" eb="4">
+      <t>×</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンジテゥ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋トレ×お酒の正しい距離感〜５選〜</t>
+    <rPh sb="3" eb="4">
+      <t>×</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タダセィ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>筋肉のためにやめてよかったこと</t>
+    <rPh sb="0" eb="1">
+      <t>キンニク</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>広島の若造の胸トレ</t>
+    <rPh sb="0" eb="2">
+      <t>ヒロシマ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ムネトル</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="182" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2633,39 +2948,60 @@
       <sz val="16"/>
       <color rgb="FF4B2FE0"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF6B7280"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF4B2FE0"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="6"/>
@@ -2708,12 +3044,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2751,11 +3087,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="38" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2790,10 +3169,47 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2801,8 +3217,20 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="0" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="パーセント" xfId="2" builtinId="5"/>
+    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3104,23 +3532,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="20" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -3128,7 +3556,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="20" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -3136,7 +3564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="20" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -3144,7 +3572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="20" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -3152,7 +3580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="20" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -3160,7 +3588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="20" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -3168,7 +3596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="30" customHeight="1">
       <c r="A12" s="13" t="s">
         <v>14</v>
       </c>
@@ -3178,7 +3606,7 @@
   <mergeCells count="1">
     <mergeCell ref="A12:B12"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3186,7 +3614,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
@@ -3200,7 +3628,7 @@
     <col min="10" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>15</v>
       </c>
@@ -3235,7 +3663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11">
       <c r="A2" s="6" t="s">
         <v>26</v>
       </c>
@@ -3270,7 +3698,7 @@
         <v>5478</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
         <v>27</v>
       </c>
@@ -3305,7 +3733,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
         <v>28</v>
       </c>
@@ -3340,7 +3768,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" ht="30" customHeight="1">
       <c r="A7" s="13" t="s">
         <v>29</v>
       </c>
@@ -3359,7 +3787,7 @@
   <mergeCells count="1">
     <mergeCell ref="A7:K7"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3367,7 +3795,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -3378,7 +3806,7 @@
     <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>30</v>
       </c>
@@ -3401,7 +3829,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -3424,7 +3852,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7">
       <c r="A3" s="6" t="s">
         <v>37</v>
       </c>
@@ -3447,7 +3875,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7">
       <c r="A4" s="6" t="s">
         <v>38</v>
       </c>
@@ -3470,7 +3898,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
         <v>39</v>
       </c>
@@ -3493,7 +3921,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7">
       <c r="A6" s="8" t="s">
         <v>40</v>
       </c>
@@ -3516,7 +3944,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7">
       <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
@@ -3539,7 +3967,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7">
       <c r="A8" s="10" t="s">
         <v>42</v>
       </c>
@@ -3562,7 +3990,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" ht="30" customHeight="1">
       <c r="A11" s="13" t="s">
         <v>43</v>
       </c>
@@ -3577,7 +4005,7 @@
   <mergeCells count="1">
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3585,7 +4013,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -3594,7 +4022,7 @@
     <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>44</v>
       </c>
@@ -3617,7 +4045,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7">
       <c r="A2" s="6" t="s">
         <v>46</v>
       </c>
@@ -3640,7 +4068,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7">
       <c r="A3" s="6" t="s">
         <v>48</v>
       </c>
@@ -3663,7 +4091,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7">
       <c r="A4" s="6" t="s">
         <v>50</v>
       </c>
@@ -3686,7 +4114,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
         <v>52</v>
       </c>
@@ -3709,7 +4137,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7">
       <c r="A6" s="6" t="s">
         <v>54</v>
       </c>
@@ -3732,7 +4160,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7">
       <c r="A7" s="6" t="s">
         <v>56</v>
       </c>
@@ -3755,7 +4183,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7">
       <c r="A8" s="8" t="s">
         <v>58</v>
       </c>
@@ -3778,7 +4206,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7">
       <c r="A9" s="8" t="s">
         <v>60</v>
       </c>
@@ -3801,7 +4229,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7">
       <c r="A10" s="6" t="s">
         <v>62</v>
       </c>
@@ -3824,7 +4252,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7">
       <c r="A11" s="6" t="s">
         <v>64</v>
       </c>
@@ -3847,7 +4275,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7">
       <c r="A12" s="6" t="s">
         <v>66</v>
       </c>
@@ -3870,7 +4298,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7">
       <c r="A13" s="6" t="s">
         <v>68</v>
       </c>
@@ -3893,7 +4321,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7">
       <c r="A14" s="10" t="s">
         <v>70</v>
       </c>
@@ -3916,7 +4344,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
         <v>72</v>
       </c>
@@ -3931,7 +4359,7 @@
   <mergeCells count="1">
     <mergeCell ref="A17:G17"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3939,21 +4367,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="17">
       <c r="A1" s="15" t="s">
         <v>73</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
     </row>
-    <row r="3" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="28" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>74</v>
       </c>
@@ -3964,7 +4392,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
         <v>77</v>
       </c>
@@ -3975,7 +4403,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
         <v>79</v>
       </c>
@@ -3986,7 +4414,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
         <v>81</v>
       </c>
@@ -3997,7 +4425,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
         <v>82</v>
       </c>
@@ -4008,7 +4436,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3">
       <c r="A8" s="10" t="s">
         <v>83</v>
       </c>
@@ -4019,7 +4447,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
         <v>85</v>
       </c>
@@ -4030,7 +4458,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="30" customHeight="1">
       <c r="A12" s="13" t="s">
         <v>87</v>
       </c>
@@ -4042,7 +4470,7 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A12:C12"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4050,9 +4478,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:U90"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="11" style="35" customWidth="1"/>
     <col min="2" max="3" width="9" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
@@ -4071,8 +4499,8 @@
     <col min="21" max="21" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:21" ht="36" customHeight="1">
+      <c r="A1" s="33" t="s">
         <v>88</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -4136,8 +4564,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:21">
+      <c r="A2" s="34" t="s">
         <v>104</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -4195,8 +4623,8 @@
       <c r="T2" s="7"/>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:21">
+      <c r="A3" s="34" t="s">
         <v>118</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -4254,8 +4682,8 @@
       <c r="T3" s="7"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:21">
+      <c r="A4" s="34" t="s">
         <v>132</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -4313,8 +4741,8 @@
       <c r="T4" s="7"/>
       <c r="U4" s="12"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:21">
+      <c r="A5" s="34" t="s">
         <v>146</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -4372,8 +4800,8 @@
       <c r="T5" s="7"/>
       <c r="U5" s="12"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:21">
+      <c r="A6" s="34" t="s">
         <v>160</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -4431,8 +4859,8 @@
       <c r="T6" s="7"/>
       <c r="U6" s="12"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:21">
+      <c r="A7" s="34" t="s">
         <v>172</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -4490,8 +4918,8 @@
       <c r="T7" s="7"/>
       <c r="U7" s="12"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:21">
+      <c r="A8" s="34" t="s">
         <v>184</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -4549,8 +4977,8 @@
       <c r="T8" s="7"/>
       <c r="U8" s="12"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:21">
+      <c r="A9" s="34" t="s">
         <v>195</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -4608,8 +5036,8 @@
       <c r="T9" s="7"/>
       <c r="U9" s="12"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:21">
+      <c r="A10" s="34" t="s">
         <v>205</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -4667,8 +5095,8 @@
       <c r="T10" s="7"/>
       <c r="U10" s="12"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:21">
+      <c r="A11" s="34" t="s">
         <v>214</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -4726,8 +5154,8 @@
       <c r="T11" s="7"/>
       <c r="U11" s="12"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:21">
+      <c r="A12" s="34" t="s">
         <v>224</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -4785,8 +5213,8 @@
       <c r="T12" s="7"/>
       <c r="U12" s="12"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:21">
+      <c r="A13" s="34" t="s">
         <v>234</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -4844,8 +5272,8 @@
       <c r="T13" s="7"/>
       <c r="U13" s="12"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:21">
+      <c r="A14" s="34" t="s">
         <v>243</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -4903,8 +5331,8 @@
       <c r="T14" s="7"/>
       <c r="U14" s="12"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:21">
+      <c r="A15" s="34" t="s">
         <v>252</v>
       </c>
       <c r="B15" s="7" t="s">
@@ -4962,8 +5390,8 @@
       <c r="T15" s="7"/>
       <c r="U15" s="12"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:21">
+      <c r="A16" s="34" t="s">
         <v>262</v>
       </c>
       <c r="B16" s="7" t="s">
@@ -5021,8 +5449,8 @@
       <c r="T16" s="7"/>
       <c r="U16" s="12"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:21">
+      <c r="A17" s="34" t="s">
         <v>271</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -5080,8 +5508,8 @@
       <c r="T17" s="7"/>
       <c r="U17" s="12"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:21">
+      <c r="A18" s="34" t="s">
         <v>279</v>
       </c>
       <c r="B18" s="7" t="s">
@@ -5139,8 +5567,8 @@
       <c r="T18" s="7"/>
       <c r="U18" s="12"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:21">
+      <c r="A19" s="34" t="s">
         <v>287</v>
       </c>
       <c r="B19" s="7" t="s">
@@ -5198,8 +5626,8 @@
       <c r="T19" s="7"/>
       <c r="U19" s="12"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:21">
+      <c r="A20" s="34" t="s">
         <v>296</v>
       </c>
       <c r="B20" s="7" t="s">
@@ -5257,8 +5685,8 @@
       <c r="T20" s="7"/>
       <c r="U20" s="12"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:21">
+      <c r="A21" s="34" t="s">
         <v>305</v>
       </c>
       <c r="B21" s="7" t="s">
@@ -5316,8 +5744,8 @@
       <c r="T21" s="7"/>
       <c r="U21" s="12"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:21">
+      <c r="A22" s="34" t="s">
         <v>314</v>
       </c>
       <c r="B22" s="7" t="s">
@@ -5375,8 +5803,8 @@
       <c r="T22" s="7"/>
       <c r="U22" s="12"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:21">
+      <c r="A23" s="34" t="s">
         <v>322</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -5434,8 +5862,8 @@
       <c r="T23" s="7"/>
       <c r="U23" s="12"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:21">
+      <c r="A24" s="34" t="s">
         <v>329</v>
       </c>
       <c r="B24" s="7" t="s">
@@ -5493,8 +5921,8 @@
       <c r="T24" s="7"/>
       <c r="U24" s="12"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:21">
+      <c r="A25" s="34" t="s">
         <v>338</v>
       </c>
       <c r="B25" s="7" t="s">
@@ -5552,8 +5980,8 @@
       <c r="T25" s="7"/>
       <c r="U25" s="12"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:21">
+      <c r="A26" s="34" t="s">
         <v>345</v>
       </c>
       <c r="B26" s="7" t="s">
@@ -5611,8 +6039,8 @@
       <c r="T26" s="7"/>
       <c r="U26" s="12"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:21">
+      <c r="A27" s="34" t="s">
         <v>354</v>
       </c>
       <c r="B27" s="7" t="s">
@@ -5670,8 +6098,8 @@
       <c r="T27" s="7"/>
       <c r="U27" s="12"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:21">
+      <c r="A28" s="34" t="s">
         <v>362</v>
       </c>
       <c r="B28" s="7" t="s">
@@ -5729,8 +6157,8 @@
       <c r="T28" s="7"/>
       <c r="U28" s="12"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:21">
+      <c r="A29" s="34" t="s">
         <v>367</v>
       </c>
       <c r="B29" s="7" t="s">
@@ -5788,8 +6216,8 @@
       <c r="T29" s="7"/>
       <c r="U29" s="12"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:21">
+      <c r="A30" s="34" t="s">
         <v>374</v>
       </c>
       <c r="B30" s="7" t="s">
@@ -5847,8 +6275,8 @@
       <c r="T30" s="7"/>
       <c r="U30" s="12"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:21">
+      <c r="A31" s="34" t="s">
         <v>379</v>
       </c>
       <c r="B31" s="7" t="s">
@@ -5906,8 +6334,8 @@
       <c r="T31" s="7"/>
       <c r="U31" s="12"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:21">
+      <c r="A32" s="34" t="s">
         <v>387</v>
       </c>
       <c r="B32" s="7" t="s">
@@ -5965,8 +6393,8 @@
       <c r="T32" s="7"/>
       <c r="U32" s="12"/>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:21">
+      <c r="A33" s="34" t="s">
         <v>397</v>
       </c>
       <c r="B33" s="7" t="s">
@@ -6024,8 +6452,8 @@
       <c r="T33" s="7"/>
       <c r="U33" s="12"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:21">
+      <c r="A34" s="34" t="s">
         <v>406</v>
       </c>
       <c r="B34" s="7" t="s">
@@ -6083,8 +6511,8 @@
       <c r="T34" s="7"/>
       <c r="U34" s="12"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:21">
+      <c r="A35" s="34" t="s">
         <v>414</v>
       </c>
       <c r="B35" s="7" t="s">
@@ -6142,8 +6570,8 @@
       <c r="T35" s="7"/>
       <c r="U35" s="12"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:21">
+      <c r="A36" s="34" t="s">
         <v>420</v>
       </c>
       <c r="B36" s="7" t="s">
@@ -6201,8 +6629,8 @@
       <c r="T36" s="7"/>
       <c r="U36" s="12"/>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:21">
+      <c r="A37" s="34" t="s">
         <v>428</v>
       </c>
       <c r="B37" s="7" t="s">
@@ -6260,8 +6688,8 @@
       <c r="T37" s="7"/>
       <c r="U37" s="12"/>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:21">
+      <c r="A38" s="34" t="s">
         <v>437</v>
       </c>
       <c r="B38" s="7" t="s">
@@ -6319,8 +6747,8 @@
       <c r="T38" s="7"/>
       <c r="U38" s="12"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:21">
+      <c r="A39" s="34" t="s">
         <v>446</v>
       </c>
       <c r="B39" s="7" t="s">
@@ -6378,8 +6806,8 @@
       <c r="T39" s="7"/>
       <c r="U39" s="12"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:21">
+      <c r="A40" s="34" t="s">
         <v>455</v>
       </c>
       <c r="B40" s="7" t="s">
@@ -6437,8 +6865,8 @@
       <c r="T40" s="7"/>
       <c r="U40" s="12"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A41" s="7" t="s">
+    <row r="41" spans="1:21">
+      <c r="A41" s="34" t="s">
         <v>464</v>
       </c>
       <c r="B41" s="7" t="s">
@@ -6496,8 +6924,8 @@
       <c r="T41" s="7"/>
       <c r="U41" s="12"/>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:21">
+      <c r="A42" s="34" t="s">
         <v>472</v>
       </c>
       <c r="B42" s="7" t="s">
@@ -6555,8 +6983,8 @@
       <c r="T42" s="7"/>
       <c r="U42" s="12"/>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A43" s="7" t="s">
+    <row r="43" spans="1:21">
+      <c r="A43" s="34" t="s">
         <v>483</v>
       </c>
       <c r="B43" s="7" t="s">
@@ -6614,8 +7042,8 @@
       <c r="T43" s="7"/>
       <c r="U43" s="12"/>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A44" s="7" t="s">
+    <row r="44" spans="1:21">
+      <c r="A44" s="34" t="s">
         <v>492</v>
       </c>
       <c r="B44" s="7" t="s">
@@ -6673,8 +7101,8 @@
       <c r="T44" s="7"/>
       <c r="U44" s="12"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A45" s="7" t="s">
+    <row r="45" spans="1:21">
+      <c r="A45" s="34" t="s">
         <v>498</v>
       </c>
       <c r="B45" s="7" t="s">
@@ -6732,8 +7160,8 @@
       <c r="T45" s="7"/>
       <c r="U45" s="12"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A46" s="7" t="s">
+    <row r="46" spans="1:21">
+      <c r="A46" s="34" t="s">
         <v>504</v>
       </c>
       <c r="B46" s="7" t="s">
@@ -6791,8 +7219,8 @@
       <c r="T46" s="7"/>
       <c r="U46" s="12"/>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A47" s="7" t="s">
+    <row r="47" spans="1:21">
+      <c r="A47" s="34" t="s">
         <v>512</v>
       </c>
       <c r="B47" s="7" t="s">
@@ -6850,8 +7278,8 @@
       <c r="T47" s="7"/>
       <c r="U47" s="12"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A48" s="7" t="s">
+    <row r="48" spans="1:21">
+      <c r="A48" s="34" t="s">
         <v>520</v>
       </c>
       <c r="B48" s="7" t="s">
@@ -6909,8 +7337,8 @@
       <c r="T48" s="7"/>
       <c r="U48" s="12"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A49" s="7" t="s">
+    <row r="49" spans="1:21">
+      <c r="A49" s="34" t="s">
         <v>525</v>
       </c>
       <c r="B49" s="7" t="s">
@@ -6968,8 +7396,8 @@
       <c r="T49" s="7"/>
       <c r="U49" s="12"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A50" s="7" t="s">
+    <row r="50" spans="1:21">
+      <c r="A50" s="34" t="s">
         <v>532</v>
       </c>
       <c r="B50" s="7" t="s">
@@ -7027,8 +7455,8 @@
       <c r="T50" s="7"/>
       <c r="U50" s="12"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A51" s="7" t="s">
+    <row r="51" spans="1:21">
+      <c r="A51" s="34" t="s">
         <v>537</v>
       </c>
       <c r="B51" s="7" t="s">
@@ -7086,8 +7514,8 @@
       <c r="T51" s="7"/>
       <c r="U51" s="12"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A52" s="7" t="s">
+    <row r="52" spans="1:21">
+      <c r="A52" s="34" t="s">
         <v>543</v>
       </c>
       <c r="B52" s="7" t="s">
@@ -7145,8 +7573,8 @@
       <c r="T52" s="7"/>
       <c r="U52" s="12"/>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A53" s="7" t="s">
+    <row r="53" spans="1:21">
+      <c r="A53" s="34" t="s">
         <v>549</v>
       </c>
       <c r="B53" s="7" t="s">
@@ -7204,8 +7632,8 @@
       <c r="T53" s="7"/>
       <c r="U53" s="12"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A54" s="7" t="s">
+    <row r="54" spans="1:21">
+      <c r="A54" s="34" t="s">
         <v>553</v>
       </c>
       <c r="B54" s="7" t="s">
@@ -7263,8 +7691,8 @@
       <c r="T54" s="7"/>
       <c r="U54" s="12"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A55" s="7" t="s">
+    <row r="55" spans="1:21">
+      <c r="A55" s="34" t="s">
         <v>562</v>
       </c>
       <c r="B55" s="7" t="s">
@@ -7322,8 +7750,8 @@
       <c r="T55" s="7"/>
       <c r="U55" s="12"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A56" s="7" t="s">
+    <row r="56" spans="1:21">
+      <c r="A56" s="34" t="s">
         <v>566</v>
       </c>
       <c r="B56" s="7" t="s">
@@ -7381,8 +7809,8 @@
       <c r="T56" s="7"/>
       <c r="U56" s="12"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A57" s="7" t="s">
+    <row r="57" spans="1:21">
+      <c r="A57" s="34" t="s">
         <v>571</v>
       </c>
       <c r="B57" s="7" t="s">
@@ -7440,8 +7868,8 @@
       <c r="T57" s="7"/>
       <c r="U57" s="12"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A58" s="7" t="s">
+    <row r="58" spans="1:21">
+      <c r="A58" s="34" t="s">
         <v>577</v>
       </c>
       <c r="B58" s="7" t="s">
@@ -7499,8 +7927,8 @@
       <c r="T58" s="7"/>
       <c r="U58" s="12"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A59" s="7" t="s">
+    <row r="59" spans="1:21">
+      <c r="A59" s="34" t="s">
         <v>580</v>
       </c>
       <c r="B59" s="7" t="s">
@@ -7558,8 +7986,8 @@
       <c r="T59" s="7"/>
       <c r="U59" s="12"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A60" s="7" t="s">
+    <row r="60" spans="1:21">
+      <c r="A60" s="34" t="s">
         <v>587</v>
       </c>
       <c r="B60" s="7" t="s">
@@ -7617,8 +8045,8 @@
       <c r="T60" s="7"/>
       <c r="U60" s="12"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A61" s="7" t="s">
+    <row r="61" spans="1:21">
+      <c r="A61" s="34" t="s">
         <v>592</v>
       </c>
       <c r="B61" s="7" t="s">
@@ -7676,8 +8104,8 @@
       <c r="T61" s="7"/>
       <c r="U61" s="12"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A62" s="7" t="s">
+    <row r="62" spans="1:21">
+      <c r="A62" s="34" t="s">
         <v>598</v>
       </c>
       <c r="B62" s="7" t="s">
@@ -7735,8 +8163,8 @@
       <c r="T62" s="7"/>
       <c r="U62" s="12"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A63" s="7" t="s">
+    <row r="63" spans="1:21">
+      <c r="A63" s="34" t="s">
         <v>603</v>
       </c>
       <c r="B63" s="7" t="s">
@@ -7794,8 +8222,8 @@
       <c r="T63" s="7"/>
       <c r="U63" s="12"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A64" s="7" t="s">
+    <row r="64" spans="1:21">
+      <c r="A64" s="34" t="s">
         <v>611</v>
       </c>
       <c r="B64" s="7" t="s">
@@ -7853,8 +8281,8 @@
       <c r="T64" s="7"/>
       <c r="U64" s="12"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A65" s="7" t="s">
+    <row r="65" spans="1:21">
+      <c r="A65" s="34" t="s">
         <v>617</v>
       </c>
       <c r="B65" s="7" t="s">
@@ -7912,8 +8340,8 @@
       <c r="T65" s="7"/>
       <c r="U65" s="12"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A66" s="7" t="s">
+    <row r="66" spans="1:21">
+      <c r="A66" s="34" t="s">
         <v>621</v>
       </c>
       <c r="B66" s="7" t="s">
@@ -7971,8 +8399,8 @@
       <c r="T66" s="7"/>
       <c r="U66" s="12"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A67" s="7" t="s">
+    <row r="67" spans="1:21">
+      <c r="A67" s="34" t="s">
         <v>623</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -8030,8 +8458,8 @@
       <c r="T67" s="7"/>
       <c r="U67" s="12"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A68" s="7" t="s">
+    <row r="68" spans="1:21">
+      <c r="A68" s="34" t="s">
         <v>627</v>
       </c>
       <c r="B68" s="7" t="s">
@@ -8089,8 +8517,8 @@
       <c r="T68" s="7"/>
       <c r="U68" s="12"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A69" s="7" t="s">
+    <row r="69" spans="1:21">
+      <c r="A69" s="34" t="s">
         <v>635</v>
       </c>
       <c r="B69" s="7" t="s">
@@ -8148,8 +8576,8 @@
       <c r="T69" s="7"/>
       <c r="U69" s="12"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A70" s="7" t="s">
+    <row r="70" spans="1:21">
+      <c r="A70" s="34" t="s">
         <v>643</v>
       </c>
       <c r="B70" s="7" t="s">
@@ -8207,8 +8635,8 @@
       <c r="T70" s="7"/>
       <c r="U70" s="12"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A71" s="7" t="s">
+    <row r="71" spans="1:21">
+      <c r="A71" s="34" t="s">
         <v>651</v>
       </c>
       <c r="B71" s="7" t="s">
@@ -8266,8 +8694,8 @@
       <c r="T71" s="7"/>
       <c r="U71" s="12"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A72" s="7" t="s">
+    <row r="72" spans="1:21">
+      <c r="A72" s="34" t="s">
         <v>658</v>
       </c>
       <c r="B72" s="7" t="s">
@@ -8325,8 +8753,8 @@
       <c r="T72" s="7"/>
       <c r="U72" s="12"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A73" s="7" t="s">
+    <row r="73" spans="1:21">
+      <c r="A73" s="34" t="s">
         <v>663</v>
       </c>
       <c r="B73" s="7" t="s">
@@ -8384,8 +8812,8 @@
       <c r="T73" s="7"/>
       <c r="U73" s="12"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A74" s="7" t="s">
+    <row r="74" spans="1:21">
+      <c r="A74" s="34" t="s">
         <v>667</v>
       </c>
       <c r="B74" s="7" t="s">
@@ -8443,8 +8871,8 @@
       <c r="T74" s="7"/>
       <c r="U74" s="12"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A75" s="7" t="s">
+    <row r="75" spans="1:21">
+      <c r="A75" s="34" t="s">
         <v>673</v>
       </c>
       <c r="B75" s="7" t="s">
@@ -8502,8 +8930,8 @@
       <c r="T75" s="7"/>
       <c r="U75" s="12"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A76" s="7" t="s">
+    <row r="76" spans="1:21">
+      <c r="A76" s="34" t="s">
         <v>678</v>
       </c>
       <c r="B76" s="7" t="s">
@@ -8561,8 +8989,8 @@
       <c r="T76" s="7"/>
       <c r="U76" s="12"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A77" s="7" t="s">
+    <row r="77" spans="1:21">
+      <c r="A77" s="34" t="s">
         <v>685</v>
       </c>
       <c r="B77" s="7" t="s">
@@ -8620,8 +9048,8 @@
       <c r="T77" s="7"/>
       <c r="U77" s="12"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A78" s="7" t="s">
+    <row r="78" spans="1:21">
+      <c r="A78" s="34" t="s">
         <v>690</v>
       </c>
       <c r="B78" s="7" t="s">
@@ -8679,8 +9107,8 @@
       <c r="T78" s="7"/>
       <c r="U78" s="12"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A79" s="7" t="s">
+    <row r="79" spans="1:21">
+      <c r="A79" s="34" t="s">
         <v>696</v>
       </c>
       <c r="B79" s="7" t="s">
@@ -8738,8 +9166,8 @@
       <c r="T79" s="7"/>
       <c r="U79" s="12"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A80" s="7" t="s">
+    <row r="80" spans="1:21">
+      <c r="A80" s="34" t="s">
         <v>698</v>
       </c>
       <c r="B80" s="7" t="s">
@@ -8797,8 +9225,8 @@
       <c r="T80" s="7"/>
       <c r="U80" s="12"/>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A81" s="7" t="s">
+    <row r="81" spans="1:21">
+      <c r="A81" s="34" t="s">
         <v>705</v>
       </c>
       <c r="B81" s="7" t="s">
@@ -8856,8 +9284,8 @@
       <c r="T81" s="7"/>
       <c r="U81" s="12"/>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A82" s="7" t="s">
+    <row r="82" spans="1:21">
+      <c r="A82" s="34" t="s">
         <v>710</v>
       </c>
       <c r="B82" s="7" t="s">
@@ -8915,8 +9343,8 @@
       <c r="T82" s="7"/>
       <c r="U82" s="12"/>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A83" s="7" t="s">
+    <row r="83" spans="1:21">
+      <c r="A83" s="34" t="s">
         <v>713</v>
       </c>
       <c r="B83" s="7" t="s">
@@ -8974,8 +9402,8 @@
       <c r="T83" s="7"/>
       <c r="U83" s="12"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A84" s="7" t="s">
+    <row r="84" spans="1:21">
+      <c r="A84" s="34" t="s">
         <v>718</v>
       </c>
       <c r="B84" s="7" t="s">
@@ -9033,8 +9461,8 @@
       <c r="T84" s="7"/>
       <c r="U84" s="12"/>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A85" s="7" t="s">
+    <row r="85" spans="1:21">
+      <c r="A85" s="34" t="s">
         <v>725</v>
       </c>
       <c r="B85" s="7" t="s">
@@ -9092,8 +9520,8 @@
       <c r="T85" s="7"/>
       <c r="U85" s="12"/>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A86" s="7" t="s">
+    <row r="86" spans="1:21">
+      <c r="A86" s="34" t="s">
         <v>733</v>
       </c>
       <c r="B86" s="7" t="s">
@@ -9151,8 +9579,8 @@
       <c r="T86" s="7"/>
       <c r="U86" s="12"/>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A87" s="7" t="s">
+    <row r="87" spans="1:21">
+      <c r="A87" s="34" t="s">
         <v>741</v>
       </c>
       <c r="B87" s="7" t="s">
@@ -9210,8 +9638,8 @@
       <c r="T87" s="7"/>
       <c r="U87" s="12"/>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A88" s="7" t="s">
+    <row r="88" spans="1:21">
+      <c r="A88" s="34" t="s">
         <v>749</v>
       </c>
       <c r="B88" s="7" t="s">
@@ -9269,8 +9697,8 @@
       <c r="T88" s="7"/>
       <c r="U88" s="12"/>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A89" s="7" t="s">
+    <row r="89" spans="1:21">
+      <c r="A89" s="34" t="s">
         <v>758</v>
       </c>
       <c r="B89" s="7" t="s">
@@ -9328,8 +9756,8 @@
       <c r="T89" s="7"/>
       <c r="U89" s="12"/>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A90" s="7" t="s">
+    <row r="90" spans="1:21">
+      <c r="A90" s="34" t="s">
         <v>767</v>
       </c>
       <c r="B90" s="7" t="s">
@@ -9388,836 +9816,3499 @@
       <c r="U90" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B00CA0B-4959-4231-8851-7068F83FFD76}">
-  <dimension ref="A1:AH425"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA6FA26-54CA-4F4C-A7A6-F11042F6B937}">
+  <dimension ref="A1:AR32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.875" style="16" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="16"/>
-    <col min="4" max="4" width="13" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.875" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="16"/>
-    <col min="11" max="11" width="9.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.375" style="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.25" style="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.75" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9" style="16"/>
-    <col min="22" max="22" width="7.875" style="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="26" max="31" width="6.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.375" style="16" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="5.25" style="16" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9" style="16"/>
+    <col min="1" max="1" width="12.83203125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="16" customWidth="1"/>
+    <col min="6" max="6" width="13" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5" style="21" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5" style="21" customWidth="1"/>
+    <col min="20" max="20" width="17.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14" style="21" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7" style="21" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="7.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6" style="21" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="39" max="42" width="10.83203125" style="16"/>
+    <col min="43" max="44" width="3" style="16" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="10.83203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:44" s="31" customFormat="1" ht="20" customHeight="1">
+      <c r="A1" s="24" t="s">
         <v>776</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="25" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="28" t="s">
+        <v>788</v>
+      </c>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="30" t="s">
+        <v>793</v>
+      </c>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="28" t="s">
+        <v>801</v>
+      </c>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+    </row>
+    <row r="2" spans="1:44" s="31" customFormat="1" ht="20" customHeight="1">
+      <c r="A2" s="24"/>
+      <c r="B2" s="31" t="s">
+        <v>815</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>778</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>779</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>813</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>780</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>781</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>782</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>783</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>784</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>785</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>786</v>
+      </c>
+      <c r="M2" s="29" t="s">
         <v>787</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19" t="s">
-        <v>788</v>
-      </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19" t="s">
+      <c r="N2" s="29" t="s">
         <v>789</v>
       </c>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19" t="s">
+      <c r="O2" s="29" t="s">
+        <v>790</v>
+      </c>
+      <c r="P2" s="29" t="s">
+        <v>791</v>
+      </c>
+      <c r="Q2" s="29" t="s">
+        <v>820</v>
+      </c>
+      <c r="R2" s="29" t="s">
+        <v>792</v>
+      </c>
+      <c r="S2" s="29" t="s">
+        <v>828</v>
+      </c>
+      <c r="T2" s="31" t="s">
         <v>794</v>
       </c>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19" t="s">
+      <c r="U2" s="31" t="s">
+        <v>781</v>
+      </c>
+      <c r="V2" s="31" t="s">
+        <v>795</v>
+      </c>
+      <c r="W2" s="31" t="s">
+        <v>796</v>
+      </c>
+      <c r="X2" s="31" t="s">
+        <v>797</v>
+      </c>
+      <c r="Y2" s="31" t="s">
+        <v>798</v>
+      </c>
+      <c r="Z2" s="31" t="s">
+        <v>799</v>
+      </c>
+      <c r="AA2" s="31" t="s">
+        <v>800</v>
+      </c>
+      <c r="AB2" s="29" t="s">
         <v>802</v>
       </c>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
-      <c r="AH1" s="19"/>
-    </row>
-    <row r="2" spans="1:34" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20" t="s">
-        <v>777</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>778</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>779</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>780</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>781</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>782</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>783</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>784</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>785</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>786</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>790</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>791</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>792</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>793</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>795</v>
-      </c>
-      <c r="Q2" s="20" t="s">
-        <v>780</v>
-      </c>
-      <c r="R2" s="20" t="s">
-        <v>796</v>
-      </c>
-      <c r="S2" s="20" t="s">
-        <v>797</v>
-      </c>
-      <c r="T2" s="20" t="s">
-        <v>798</v>
-      </c>
-      <c r="U2" s="20" t="s">
-        <v>799</v>
-      </c>
-      <c r="V2" s="20" t="s">
-        <v>800</v>
-      </c>
-      <c r="W2" s="20" t="s">
-        <v>801</v>
-      </c>
-      <c r="X2" s="20" t="s">
+      <c r="AC2" s="29" t="s">
         <v>803</v>
       </c>
-      <c r="Y2" s="20" t="s">
+      <c r="AD2" s="29" t="s">
         <v>804</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AE2" s="29" t="s">
         <v>805</v>
       </c>
-      <c r="AA2" s="20" t="s">
+      <c r="AF2" s="29" t="s">
         <v>806</v>
       </c>
-      <c r="AB2" s="20" t="s">
+      <c r="AG2" s="29" t="s">
         <v>807</v>
       </c>
-      <c r="AC2" s="20" t="s">
+      <c r="AH2" s="29" t="s">
         <v>808</v>
       </c>
-      <c r="AD2" s="20" t="s">
+      <c r="AI2" s="29" t="s">
         <v>809</v>
       </c>
-      <c r="AE2" s="20" t="s">
+      <c r="AJ2" s="29" t="s">
         <v>810</v>
       </c>
-      <c r="AF2" s="20" t="s">
+      <c r="AK2" s="29" t="s">
         <v>811</v>
       </c>
-      <c r="AG2" s="20" t="s">
+      <c r="AL2" s="29" t="s">
         <v>812</v>
       </c>
-      <c r="AH2" s="20" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="17">
+      <c r="AQ2" s="31">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" ht="20" customHeight="1">
+      <c r="A3" s="19">
         <v>46293</v>
       </c>
-      <c r="B3" s="16">
-        <v>4308</v>
-      </c>
-      <c r="C3" s="16">
-        <v>3358</v>
-      </c>
-      <c r="D3" s="16">
+      <c r="B3" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4349</v>
+      </c>
+      <c r="D3" s="22">
+        <v>3381</v>
+      </c>
+      <c r="E3" s="18">
+        <v>1.1805555555555555E-2</v>
+      </c>
+      <c r="F3" s="16">
         <v>8</v>
       </c>
-      <c r="E3" s="16">
+      <c r="G3" s="16">
         <v>6</v>
       </c>
-      <c r="F3" s="16">
-        <v>52.9</v>
-      </c>
-      <c r="G3" s="16">
-        <v>0</v>
-      </c>
-      <c r="H3" s="16">
-        <v>0.8</v>
-      </c>
-      <c r="I3" s="16">
-        <v>0.4</v>
-      </c>
-      <c r="J3" s="16">
-        <v>0</v>
-      </c>
-      <c r="K3" s="16">
-        <v>0</v>
-      </c>
-      <c r="L3" s="16">
-        <v>42.3</v>
-      </c>
-      <c r="M3" s="16">
-        <v>38.5</v>
-      </c>
-      <c r="N3" s="16">
-        <v>18.5</v>
-      </c>
-      <c r="O3" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="P3" s="16">
+      <c r="H3" s="21">
+        <v>0.53</v>
+      </c>
+      <c r="I3" s="21">
+        <v>0</v>
+      </c>
+      <c r="J3" s="21">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="K3" s="21">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L3" s="21">
+        <v>0</v>
+      </c>
+      <c r="M3" s="21">
+        <v>0</v>
+      </c>
+      <c r="N3" s="21">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="O3" s="21">
+        <v>0.39</v>
+      </c>
+      <c r="P3" s="21">
+        <v>0.183</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>821</v>
+      </c>
+      <c r="R3" s="21">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="T3" s="16">
         <v>34</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="U3" s="16">
         <v>6</v>
       </c>
-      <c r="R3" s="16">
+      <c r="V3" s="16">
         <v>1</v>
       </c>
-      <c r="S3" s="16">
+      <c r="W3" s="16">
         <v>27</v>
       </c>
-      <c r="T3" s="16">
-        <v>0</v>
-      </c>
-      <c r="U3" s="16">
-        <v>0</v>
-      </c>
-      <c r="V3" s="16">
-        <v>0</v>
-      </c>
-      <c r="W3" s="16">
+      <c r="X3" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA3" s="16">
         <v>12</v>
       </c>
-      <c r="X3" s="16">
-        <v>11.7</v>
-      </c>
-      <c r="Y3" s="16">
-        <v>88.3</v>
-      </c>
-      <c r="Z3" s="16">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AA3" s="16">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="AB3" s="16">
-        <v>28.1</v>
-      </c>
-      <c r="AC3" s="16">
-        <v>21.7</v>
-      </c>
-      <c r="AD3" s="16">
-        <v>19.5</v>
-      </c>
-      <c r="AE3" s="16">
+      <c r="AB3" s="21">
+        <v>0.121</v>
+      </c>
+      <c r="AC3" s="21">
+        <v>0.879</v>
+      </c>
+      <c r="AD3" s="21">
+        <v>2.3E-2</v>
+      </c>
+      <c r="AE3" s="21">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="AF3" s="21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AG3" s="21">
+        <v>0.217</v>
+      </c>
+      <c r="AH3" s="21">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="AI3" s="21">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="AJ3" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="AK3" s="21">
+        <v>0.99</v>
+      </c>
+      <c r="AL3" s="21">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" ht="20" customHeight="1">
+      <c r="A4" s="19">
+        <v>46289</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4090</v>
+      </c>
+      <c r="D4" s="22">
+        <v>3116</v>
+      </c>
+      <c r="E4" s="18">
+        <v>1.1805555555555555E-2</v>
+      </c>
+      <c r="F4" s="16">
+        <v>7</v>
+      </c>
+      <c r="G4" s="16">
+        <v>2</v>
+      </c>
+      <c r="H4" s="21">
+        <v>0.441</v>
+      </c>
+      <c r="I4" s="21">
+        <v>0</v>
+      </c>
+      <c r="J4" s="21">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="K4" s="21">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="L4" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="M4" s="21">
+        <v>0</v>
+      </c>
+      <c r="N4" s="21">
+        <v>0.45</v>
+      </c>
+      <c r="O4" s="21">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="P4" s="21">
+        <v>0.16</v>
+      </c>
+      <c r="Q4" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="R4" s="21">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="S4" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="T4" s="16">
+        <v>38</v>
+      </c>
+      <c r="U4" s="16">
+        <v>2</v>
+      </c>
+      <c r="V4" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="W4" s="16">
+        <v>20</v>
+      </c>
+      <c r="X4" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="16">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA4" s="16">
+        <v>15</v>
+      </c>
+      <c r="AB4" s="21">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="AC4" s="21">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AD4" s="21">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="AE4" s="21">
+        <v>0.249</v>
+      </c>
+      <c r="AF4" s="21">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="AG4" s="21">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="AH4" s="21">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="AI4" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AJ4" s="21">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="AK4" s="21">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="AL4" s="21">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44" ht="20" customHeight="1">
+      <c r="A5" s="19">
+        <v>46219</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="C5" s="22">
+        <v>2130</v>
+      </c>
+      <c r="D5" s="22">
+        <v>1533</v>
+      </c>
+      <c r="E5" s="18">
+        <v>5.4166666666666669E-2</v>
+      </c>
+      <c r="F5" s="16">
         <v>9</v>
       </c>
-      <c r="AF3" s="16">
-        <v>1.6</v>
-      </c>
-      <c r="AG3" s="16">
-        <v>99.1</v>
-      </c>
-      <c r="AH3" s="16">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="17">
-        <v>46292</v>
-      </c>
-      <c r="B4" s="16">
-        <v>4062</v>
-      </c>
-      <c r="C4" s="16">
-        <v>3098</v>
-      </c>
-      <c r="D4" s="16">
+      <c r="G5" s="16">
+        <v>1</v>
+      </c>
+      <c r="H5" s="21">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="I5" s="21">
+        <v>0</v>
+      </c>
+      <c r="J5" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="K5" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L5" s="21">
+        <v>0</v>
+      </c>
+      <c r="M5" s="21">
+        <v>0</v>
+      </c>
+      <c r="N5" s="21">
+        <v>0.221</v>
+      </c>
+      <c r="O5" s="21">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="P5" s="21">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="Q5" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="R5" s="21">
+        <v>0.18</v>
+      </c>
+      <c r="S5" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="T5" s="16">
+        <v>20</v>
+      </c>
+      <c r="U5" s="16">
+        <v>1</v>
+      </c>
+      <c r="V5" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="W5" s="16">
+        <v>26</v>
+      </c>
+      <c r="X5" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="16">
+        <v>4</v>
+      </c>
+      <c r="AB5" s="21">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="AC5" s="21">
+        <v>0.70099999999999996</v>
+      </c>
+      <c r="AD5" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="AE5" s="21">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="AF5" s="21">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="AG5" s="21">
+        <v>0.183</v>
+      </c>
+      <c r="AH5" s="21">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="AI5" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AJ5" s="21">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AK5" s="21">
+        <v>0.96</v>
+      </c>
+      <c r="AL5" s="21">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" ht="20" customHeight="1">
+      <c r="A6" s="19">
+        <v>46198</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="C6" s="22">
+        <v>2598</v>
+      </c>
+      <c r="D6" s="22">
+        <v>737</v>
+      </c>
+      <c r="E6" s="18">
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="F6" s="16">
+        <v>6</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="I6" s="21">
+        <v>0</v>
+      </c>
+      <c r="J6" s="21">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="K6" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L6" s="21">
+        <v>0</v>
+      </c>
+      <c r="M6" s="21">
+        <v>0</v>
+      </c>
+      <c r="N6" s="21">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="O6" s="21">
+        <v>0.34</v>
+      </c>
+      <c r="P6" s="21">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="Q6" s="21">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="R6" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="S6" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="T6" s="16">
+        <v>22</v>
+      </c>
+      <c r="U6" s="16">
+        <v>1</v>
+      </c>
+      <c r="V6" s="16">
+        <v>0</v>
+      </c>
+      <c r="W6" s="16">
+        <v>34</v>
+      </c>
+      <c r="X6" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA6" s="16">
+        <v>5</v>
+      </c>
+      <c r="AB6" s="21">
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="AC6" s="21">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="AD6" s="21">
+        <v>2.4E-2</v>
+      </c>
+      <c r="AE6" s="21">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="AF6" s="21">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="AG6" s="21">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="AH6" s="21">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="AI6" s="21">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AJ6" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="AK6" s="21">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="AL6" s="21">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" ht="20" customHeight="1">
+      <c r="A7" s="19">
+        <v>46192</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>822</v>
+      </c>
+      <c r="C7" s="22">
+        <v>2669</v>
+      </c>
+      <c r="D7" s="22">
+        <v>413</v>
+      </c>
+      <c r="E7" s="18">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="F7" s="16">
+        <v>8</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
+      <c r="H7" s="21">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="I7" s="21">
+        <v>0</v>
+      </c>
+      <c r="J7" s="21">
+        <v>1.2E-2</v>
+      </c>
+      <c r="K7" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L7" s="21">
+        <v>0</v>
+      </c>
+      <c r="M7" s="21">
+        <v>0</v>
+      </c>
+      <c r="N7" s="21">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O7" s="21">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="P7" s="21">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>823</v>
+      </c>
+      <c r="R7" s="21">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="S7" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="T7" s="16">
+        <v>21</v>
+      </c>
+      <c r="U7" s="16">
+        <v>1</v>
+      </c>
+      <c r="V7" s="16">
+        <v>0</v>
+      </c>
+      <c r="W7" s="16">
+        <v>24</v>
+      </c>
+      <c r="X7" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="16">
+        <v>4</v>
+      </c>
+      <c r="AB7" s="21">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="AC7" s="21">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="AD7" s="21">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AE7" s="21">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="AF7" s="21">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="AG7" s="21">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="AH7" s="21">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="AI7" s="21">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AJ7" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="AK7" s="21">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="AL7" s="21">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44" ht="20" customHeight="1">
+      <c r="A8" s="19">
+        <v>46173</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>824</v>
+      </c>
+      <c r="C8" s="22">
+        <v>2061</v>
+      </c>
+      <c r="D8" s="22">
+        <v>1436</v>
+      </c>
+      <c r="E8" s="18">
+        <v>7.7083333333333337E-2</v>
+      </c>
+      <c r="F8" s="16">
         <v>7</v>
       </c>
-      <c r="E4" s="16">
+      <c r="G8" s="16">
+        <v>1</v>
+      </c>
+      <c r="H8" s="21">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K8" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L8" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="M8" s="21">
+        <v>0</v>
+      </c>
+      <c r="N8" s="21">
+        <v>5.5E-2</v>
+      </c>
+      <c r="O8" s="21">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="P8" s="21">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Q8" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="R8" s="21">
+        <v>0.443</v>
+      </c>
+      <c r="S8" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="T8" s="16">
+        <v>40</v>
+      </c>
+      <c r="U8" s="16">
+        <v>1</v>
+      </c>
+      <c r="V8" s="16">
+        <v>1</v>
+      </c>
+      <c r="W8" s="16">
+        <v>23</v>
+      </c>
+      <c r="X8" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="16">
         <v>2</v>
       </c>
-      <c r="F4" s="16">
-        <v>44.1</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0</v>
-      </c>
-      <c r="H4" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="I4" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="16">
+      <c r="Z8" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA8" s="16">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="21">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="AC8" s="21">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="AD8" s="21">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AE8" s="21">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="AF8" s="21">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="AG8" s="21">
+        <v>0.158</v>
+      </c>
+      <c r="AH8" s="21">
+        <v>0.151</v>
+      </c>
+      <c r="AI8" s="21">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AJ8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="21">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="AL8" s="21">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:44" ht="20" customHeight="1">
+      <c r="A9" s="19">
+        <v>46149</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="C9" s="22">
+        <v>2669</v>
+      </c>
+      <c r="D9" s="22">
+        <v>1830</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="F9" s="16">
+        <v>4</v>
+      </c>
+      <c r="G9" s="16">
+        <v>2</v>
+      </c>
+      <c r="H9" s="21">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="I9" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="21">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="K9" s="21">
+        <v>0</v>
+      </c>
+      <c r="L9" s="21">
+        <v>0</v>
+      </c>
+      <c r="M9" s="21">
+        <v>0</v>
+      </c>
+      <c r="N9" s="21">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="O9" s="21">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="P9" s="21">
+        <v>1.9E-2</v>
+      </c>
+      <c r="Q9" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="R9" s="21">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="S9" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="T9" s="16">
+        <v>21</v>
+      </c>
+      <c r="U9" s="16">
+        <v>2</v>
+      </c>
+      <c r="V9" s="16">
+        <v>1</v>
+      </c>
+      <c r="W9" s="16">
+        <v>30</v>
+      </c>
+      <c r="X9" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA9" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="21">
+        <v>0.32</v>
+      </c>
+      <c r="AC9" s="21">
+        <v>0.68</v>
+      </c>
+      <c r="AD9" s="21">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AE9" s="21">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="AF9" s="21">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="AG9" s="21">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="AH9" s="21">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="AI9" s="21">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="AJ9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="21">
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="AL9" s="21">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" ht="20" customHeight="1">
+      <c r="A10" s="19">
+        <v>46134</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="C10" s="22">
+        <v>3099</v>
+      </c>
+      <c r="D10" s="22">
+        <v>2099</v>
+      </c>
+      <c r="E10" s="18">
+        <v>5.4166666666666669E-2</v>
+      </c>
+      <c r="F10" s="16">
+        <v>12</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1</v>
+      </c>
+      <c r="H10" s="21">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="I10" s="21">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21">
+        <v>0.02</v>
+      </c>
+      <c r="K10" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L10" s="21">
+        <v>0</v>
+      </c>
+      <c r="M10" s="21">
+        <v>0</v>
+      </c>
+      <c r="N10" s="21">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="O10" s="21">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="P10" s="21">
+        <v>0.01</v>
+      </c>
+      <c r="Q10" s="21">
         <v>0.1</v>
       </c>
-      <c r="K4" s="16">
-        <v>0</v>
-      </c>
-      <c r="L4" s="16">
-        <v>44.7</v>
-      </c>
-      <c r="M4" s="16">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="N4" s="16">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="O4" s="16">
-        <v>0.8</v>
-      </c>
-      <c r="P4" s="16">
+      <c r="R10" s="21">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="S10" s="21" t="s">
+        <v>821</v>
+      </c>
+      <c r="T10" s="16">
+        <v>35</v>
+      </c>
+      <c r="U10" s="16">
+        <v>1</v>
+      </c>
+      <c r="V10" s="16">
+        <v>3</v>
+      </c>
+      <c r="W10" s="16">
+        <v>48</v>
+      </c>
+      <c r="X10" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA10" s="16">
+        <v>6</v>
+      </c>
+      <c r="AB10" s="21">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="AC10" s="21">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="AD10" s="21">
+        <v>2.3E-2</v>
+      </c>
+      <c r="AE10" s="21">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="AF10" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="AG10" s="21">
+        <v>0.156</v>
+      </c>
+      <c r="AH10" s="21">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="AI10" s="21">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AJ10" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="21">
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="AL10" s="21">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" ht="20" customHeight="1">
+      <c r="A11" s="19">
+        <v>46124</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="C11" s="22">
+        <v>6471</v>
+      </c>
+      <c r="D11" s="22">
+        <v>3708</v>
+      </c>
+      <c r="E11" s="18">
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="F11" s="16">
+        <v>6</v>
+      </c>
+      <c r="G11" s="16">
+        <v>3</v>
+      </c>
+      <c r="H11" s="21">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="I11" s="21">
+        <v>0</v>
+      </c>
+      <c r="J11" s="21">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="K11" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="L11" s="21">
+        <v>0</v>
+      </c>
+      <c r="M11" s="21">
+        <v>0</v>
+      </c>
+      <c r="N11" s="21">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="O11" s="21">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="P11" s="21">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="R11" s="21">
+        <v>0.219</v>
+      </c>
+      <c r="S11" s="21">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="T11" s="16">
+        <v>34</v>
+      </c>
+      <c r="U11" s="16">
+        <v>3</v>
+      </c>
+      <c r="V11" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="W11" s="16">
+        <v>34</v>
+      </c>
+      <c r="X11" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA11" s="16">
+        <v>4</v>
+      </c>
+      <c r="AB11" s="21">
+        <v>0.193</v>
+      </c>
+      <c r="AC11" s="21">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="AD11" s="21">
+        <v>2.4E-2</v>
+      </c>
+      <c r="AE11" s="21">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="AF11" s="21">
+        <v>0.247</v>
+      </c>
+      <c r="AG11" s="21">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="AH11" s="21">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="AI11" s="21">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="AJ11" s="21">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="AK11" s="21">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="AL11" s="21">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" ht="20" customHeight="1">
+      <c r="A12" s="19">
+        <v>46120</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="C12" s="22">
+        <v>3772</v>
+      </c>
+      <c r="D12" s="22">
+        <v>2152</v>
+      </c>
+      <c r="E12" s="18">
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="F12" s="16">
+        <v>5</v>
+      </c>
+      <c r="G12" s="16">
+        <v>5</v>
+      </c>
+      <c r="H12" s="21">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="I12" s="21">
+        <v>0</v>
+      </c>
+      <c r="J12" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="K12" s="21">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L12" s="21">
+        <v>0</v>
+      </c>
+      <c r="M12" s="21">
+        <v>0</v>
+      </c>
+      <c r="N12" s="21">
+        <v>0.126</v>
+      </c>
+      <c r="O12" s="21">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="P12" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="Q12" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="R12" s="21">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="S12" s="21">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="T12" s="16">
+        <v>7</v>
+      </c>
+      <c r="U12" s="16">
+        <v>5</v>
+      </c>
+      <c r="V12" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="W12" s="16">
+        <v>37</v>
+      </c>
+      <c r="X12" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA12" s="16">
+        <v>9</v>
+      </c>
+      <c r="AB12" s="21">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="AC12" s="21">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="AD12" s="21">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AE12" s="21">
+        <v>0.371</v>
+      </c>
+      <c r="AF12" s="21">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="AG12" s="21">
+        <v>0.152</v>
+      </c>
+      <c r="AH12" s="21">
+        <v>0.126</v>
+      </c>
+      <c r="AI12" s="21">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AJ12" s="21">
+        <v>0.01</v>
+      </c>
+      <c r="AK12" s="21">
+        <v>0.98</v>
+      </c>
+      <c r="AL12" s="21">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" ht="20" customHeight="1">
+      <c r="A13" s="19">
+        <v>46118</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="C13" s="22">
+        <v>2874</v>
+      </c>
+      <c r="D13" s="22">
+        <v>1813</v>
+      </c>
+      <c r="E13" s="18">
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="F13" s="16">
+        <v>4</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="I13" s="21">
+        <v>0</v>
+      </c>
+      <c r="J13" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="K13" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L13" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="M13" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="N13" s="21">
+        <v>0.128</v>
+      </c>
+      <c r="O13" s="21">
+        <v>0.496</v>
+      </c>
+      <c r="P13" s="21">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="Q13" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="R13" s="21">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="S13" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="T13" s="16">
+        <v>18</v>
+      </c>
+      <c r="U13" s="16">
+        <v>0</v>
+      </c>
+      <c r="V13" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="W13" s="16">
+        <v>29</v>
+      </c>
+      <c r="X13" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA13" s="16">
+        <v>3</v>
+      </c>
+      <c r="AB13" s="21">
+        <v>0.311</v>
+      </c>
+      <c r="AC13" s="21">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="AD13" s="21">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AE13" s="21">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="AF13" s="21">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="AG13" s="21">
+        <v>0.157</v>
+      </c>
+      <c r="AH13" s="21">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="AI13" s="21">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="AJ13" s="21">
+        <v>1.4E-2</v>
+      </c>
+      <c r="AK13" s="21">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AL13" s="21">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:44" ht="20" customHeight="1">
+      <c r="A14" s="19">
+        <v>46111</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>831</v>
+      </c>
+      <c r="C14" s="22">
+        <v>2397</v>
+      </c>
+      <c r="D14" s="22">
+        <v>1406</v>
+      </c>
+      <c r="E14" s="18">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="F14" s="16">
+        <v>4</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="I14" s="21">
+        <v>0</v>
+      </c>
+      <c r="J14" s="21">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="K14" s="21">
+        <v>0</v>
+      </c>
+      <c r="L14" s="21">
+        <v>0</v>
+      </c>
+      <c r="M14" s="21">
+        <v>0</v>
+      </c>
+      <c r="N14" s="21">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="O14" s="21">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="P14" s="21">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="Q14" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="R14" s="21">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="S14" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="T14" s="16">
+        <v>9</v>
+      </c>
+      <c r="U14" s="16">
+        <v>0</v>
+      </c>
+      <c r="V14" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="W14" s="16">
+        <v>16</v>
+      </c>
+      <c r="X14" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA14" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="21">
+        <v>0.377</v>
+      </c>
+      <c r="AC14" s="21">
+        <v>0.623</v>
+      </c>
+      <c r="AD14" s="21">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="AE14" s="21">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="AF14" s="21">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="AG14" s="21">
+        <v>0.152</v>
+      </c>
+      <c r="AH14" s="21">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="AI14" s="21">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AJ14" s="21">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AK14" s="21">
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="AL14" s="21">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:44" ht="20" customHeight="1">
+      <c r="A15" s="19">
+        <v>46091</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>832</v>
+      </c>
+      <c r="C15" s="22">
+        <v>8427</v>
+      </c>
+      <c r="D15" s="22">
+        <v>6737</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3.125E-2</v>
+      </c>
+      <c r="F15" s="16">
+        <v>12</v>
+      </c>
+      <c r="G15" s="16">
+        <v>2</v>
+      </c>
+      <c r="H15" s="21">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="I15" s="21">
+        <v>0</v>
+      </c>
+      <c r="J15" s="21">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="K15" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L15" s="21">
+        <v>0</v>
+      </c>
+      <c r="M15" s="21">
+        <v>0</v>
+      </c>
+      <c r="N15" s="21">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="O15" s="21">
+        <v>0.182</v>
+      </c>
+      <c r="P15" s="21">
+        <v>0.183</v>
+      </c>
+      <c r="Q15" s="21">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="R15" s="21">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="S15" s="21">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="T15" s="16">
+        <v>81</v>
+      </c>
+      <c r="U15" s="16">
+        <v>2</v>
+      </c>
+      <c r="V15" s="16">
+        <v>2</v>
+      </c>
+      <c r="W15" s="16">
+        <v>48</v>
+      </c>
+      <c r="X15" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="16">
+        <v>2</v>
+      </c>
+      <c r="Z15" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA15" s="16">
+        <v>12</v>
+      </c>
+      <c r="AB15" s="21">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="AC15" s="21">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="AD15" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AE15" s="21">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="AF15" s="21">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="AG15" s="21">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="AH15" s="21">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AI15" s="21">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="AJ15" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="AK15" s="21">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="AL15" s="21">
+        <v>0.26100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44" ht="20" customHeight="1">
+      <c r="A16" s="19">
+        <v>46090</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="C16" s="22">
+        <v>2848</v>
+      </c>
+      <c r="D16" s="22">
+        <v>1657</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="F16" s="16">
+        <v>5</v>
+      </c>
+      <c r="G16" s="16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="21">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="I16" s="21">
+        <v>0</v>
+      </c>
+      <c r="J16" s="21">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="K16" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="L16" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="M16" s="21">
+        <v>0</v>
+      </c>
+      <c r="N16" s="21">
+        <v>0.156</v>
+      </c>
+      <c r="O16" s="21">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="P16" s="21">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="Q16" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="R16" s="21">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="S16" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="T16" s="16">
+        <v>14</v>
+      </c>
+      <c r="U16" s="16">
+        <v>0</v>
+      </c>
+      <c r="V16" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="W16" s="16">
+        <v>30</v>
+      </c>
+      <c r="X16" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA16" s="16">
+        <v>2</v>
+      </c>
+      <c r="AB16" s="21">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="AC16" s="21">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="AD16" s="21">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="AE16" s="21">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="AF16" s="21">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="AG16" s="21">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="AH16" s="21">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="AI16" s="21">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AJ16" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="21">
+        <v>0.95699999999999996</v>
+      </c>
+      <c r="AL16" s="21">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" ht="20" customHeight="1">
+      <c r="A17" s="19">
+        <v>46083</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>834</v>
+      </c>
+      <c r="C17" s="22">
+        <v>4371</v>
+      </c>
+      <c r="D17" s="22">
+        <v>2566</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="F17" s="16">
+        <v>6</v>
+      </c>
+      <c r="G17" s="16">
+        <v>2</v>
+      </c>
+      <c r="H17" s="21">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="I17" s="21">
+        <v>0</v>
+      </c>
+      <c r="J17" s="21">
+        <v>1.2E-2</v>
+      </c>
+      <c r="K17" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="L17" s="21">
+        <v>0</v>
+      </c>
+      <c r="M17" s="21">
+        <v>0</v>
+      </c>
+      <c r="N17" s="21">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="O17" s="21" t="s">
+        <v>835</v>
+      </c>
+      <c r="P17" s="21">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="Q17" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="R17" s="21">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="S17" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="T17" s="16">
+        <v>19</v>
+      </c>
+      <c r="U17" s="16">
+        <v>2</v>
+      </c>
+      <c r="V17" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="W17" s="16">
+        <v>30</v>
+      </c>
+      <c r="X17" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="AA17" s="16">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="21">
+        <v>0.217</v>
+      </c>
+      <c r="AC17" s="21">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="AD17" s="21">
+        <v>2.3E-2</v>
+      </c>
+      <c r="AE17" s="21">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="AF17" s="21">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="AG17" s="21">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="AH17" s="21">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="AI17" s="21">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AJ17" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="21">
+        <v>0.97099999999999997</v>
+      </c>
+      <c r="AL17" s="21">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" ht="20" customHeight="1">
+      <c r="A18" s="19">
+        <v>46079</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>836</v>
+      </c>
+      <c r="C18" s="22">
+        <v>2647</v>
+      </c>
+      <c r="D18" s="22">
+        <v>1847</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="F18" s="16">
+        <v>4</v>
+      </c>
+      <c r="G18" s="16">
+        <v>2</v>
+      </c>
+      <c r="H18" s="21">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="I18" s="21">
+        <v>0</v>
+      </c>
+      <c r="J18" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="K18" s="21">
+        <v>0</v>
+      </c>
+      <c r="L18" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="M18" s="21">
+        <v>0</v>
+      </c>
+      <c r="N18" s="21">
+        <v>0.251</v>
+      </c>
+      <c r="O18" s="21">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="P18" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="R18" s="21">
+        <v>0.251</v>
+      </c>
+      <c r="T18" s="16">
+        <v>22</v>
+      </c>
+      <c r="U18" s="16">
+        <v>2</v>
+      </c>
+      <c r="W18" s="16">
+        <v>28</v>
+      </c>
+      <c r="X18" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="16">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="21">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="AC18" s="21">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="AD18" s="21">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="AE18" s="21">
+        <v>0.372</v>
+      </c>
+      <c r="AF18" s="21">
+        <v>0.31</v>
+      </c>
+      <c r="AG18" s="21">
+        <v>0.159</v>
+      </c>
+      <c r="AH18" s="21" t="s">
+        <v>837</v>
+      </c>
+      <c r="AI18" s="21">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="AJ18" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL18" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" ht="20" customHeight="1">
+      <c r="A19" s="19">
+        <v>46077</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>838</v>
+      </c>
+      <c r="C19" s="22">
+        <v>2910</v>
+      </c>
+      <c r="D19" s="22">
+        <v>1698</v>
+      </c>
+      <c r="E19" s="18">
+        <v>2.7777777777777779E-3</v>
+      </c>
+      <c r="F19" s="16">
+        <v>4</v>
+      </c>
+      <c r="G19" s="16">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="I19" s="21">
+        <v>0</v>
+      </c>
+      <c r="J19" s="21">
+        <v>1.4E-2</v>
+      </c>
+      <c r="K19" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L19" s="21">
+        <v>0</v>
+      </c>
+      <c r="M19" s="21">
+        <v>0</v>
+      </c>
+      <c r="N19" s="21">
+        <v>0.155</v>
+      </c>
+      <c r="O19" s="21">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="P19" s="21">
+        <v>4.7E-2</v>
+      </c>
+      <c r="R19" s="21">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="T19" s="16">
+        <v>14</v>
+      </c>
+      <c r="U19" s="16">
+        <v>0</v>
+      </c>
+      <c r="V19" s="16">
+        <v>1</v>
+      </c>
+      <c r="W19" s="16">
+        <v>24</v>
+      </c>
+      <c r="X19" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="16">
+        <v>3</v>
+      </c>
+      <c r="AB19" s="21">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="AC19" s="21">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="AD19" s="21">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AE19" s="21">
+        <v>0.34</v>
+      </c>
+      <c r="AF19" s="21">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="AG19" s="21">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="AH19" s="21">
+        <v>7.8E-2</v>
+      </c>
+      <c r="AI19" s="21">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="AJ19" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" ht="20" customHeight="1">
+      <c r="A20" s="19">
+        <v>46075</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>839</v>
+      </c>
+      <c r="C20" s="22">
+        <v>2406</v>
+      </c>
+      <c r="D20" s="22">
+        <v>1550</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="F20" s="16">
+        <v>4</v>
+      </c>
+      <c r="G20" s="16">
+        <v>0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="I20" s="21">
+        <v>0</v>
+      </c>
+      <c r="J20" s="21">
+        <v>1.9E-2</v>
+      </c>
+      <c r="K20" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="L20" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="M20" s="21">
+        <v>0</v>
+      </c>
+      <c r="N20" s="21">
+        <v>0.17</v>
+      </c>
+      <c r="O20" s="21">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="P20" s="21">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="R20" s="21">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="S20" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="T20" s="16">
+        <v>15</v>
+      </c>
+      <c r="U20" s="16">
+        <v>0</v>
+      </c>
+      <c r="V20" s="16">
+        <v>1</v>
+      </c>
+      <c r="W20" s="16">
+        <v>28</v>
+      </c>
+      <c r="X20" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="16">
+        <v>2</v>
+      </c>
+      <c r="AA20" s="16">
+        <v>2</v>
+      </c>
+      <c r="AB20" s="21">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="AC20" s="21">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="AD20" s="21">
+        <v>0.02</v>
+      </c>
+      <c r="AE20" s="21">
+        <v>0.36</v>
+      </c>
+      <c r="AF20" s="21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AG20" s="21">
+        <v>0.16</v>
+      </c>
+      <c r="AH20" s="21">
+        <v>0.12</v>
+      </c>
+      <c r="AI20" s="21">
+        <v>0.06</v>
+      </c>
+      <c r="AJ20" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL20" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" ht="20" customHeight="1">
+      <c r="A21" s="19">
+        <v>46069</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="C21" s="22">
+        <v>112260</v>
+      </c>
+      <c r="D21" s="22">
+        <v>49995</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="F21" s="16">
+        <v>12</v>
+      </c>
+      <c r="G21" s="16">
+        <v>69</v>
+      </c>
+      <c r="H21" s="21">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="I21" s="21">
+        <v>0</v>
+      </c>
+      <c r="J21" s="21">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="K21" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L21" s="21">
+        <v>0</v>
+      </c>
+      <c r="M21" s="21">
+        <v>0</v>
+      </c>
+      <c r="N21" s="21">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="O21" s="21">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="P21" s="21">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="R21" s="21">
+        <v>1.2E-2</v>
+      </c>
+      <c r="S21" s="21">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="T21" s="16">
+        <v>561</v>
+      </c>
+      <c r="U21" s="16">
+        <v>69</v>
+      </c>
+      <c r="V21" s="16">
+        <v>2</v>
+      </c>
+      <c r="W21" s="16">
+        <v>407</v>
+      </c>
+      <c r="X21" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="16">
+        <v>11</v>
+      </c>
+      <c r="AA21" s="16">
+        <v>153</v>
+      </c>
+      <c r="AB21" s="21">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="AC21" s="21">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="AD21" s="21">
+        <v>0.05</v>
+      </c>
+      <c r="AE21" s="21">
+        <v>0.433</v>
+      </c>
+      <c r="AF21" s="21">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="AG21" s="21">
+        <v>0.124</v>
+      </c>
+      <c r="AH21" s="21">
+        <v>0.05</v>
+      </c>
+      <c r="AI21" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AJ21" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL21" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" ht="20" customHeight="1">
+      <c r="A22" s="19">
+        <v>46048</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>841</v>
+      </c>
+      <c r="C22" s="22">
+        <v>2882</v>
+      </c>
+      <c r="D22" s="22">
+        <v>2213</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3.1944444444444442E-2</v>
+      </c>
+      <c r="F22" s="16">
+        <v>9</v>
+      </c>
+      <c r="G22" s="16">
+        <v>2</v>
+      </c>
+      <c r="H22" s="21">
+        <v>0.499</v>
+      </c>
+      <c r="I22" s="21">
+        <v>0</v>
+      </c>
+      <c r="J22" s="21">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="K22" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="L22" s="21">
+        <v>0</v>
+      </c>
+      <c r="M22" s="21">
+        <v>0</v>
+      </c>
+      <c r="N22" s="21">
+        <v>0.189</v>
+      </c>
+      <c r="O22" s="21">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="P22" s="21">
+        <v>0.06</v>
+      </c>
+      <c r="Q22" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="R22" s="21">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="T22" s="16">
+        <v>18</v>
+      </c>
+      <c r="U22" s="16">
+        <v>2</v>
+      </c>
+      <c r="V22" s="16">
+        <v>1</v>
+      </c>
+      <c r="W22" s="16">
+        <v>48</v>
+      </c>
+      <c r="X22" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="16">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="16">
+        <v>4</v>
+      </c>
+      <c r="AB22" s="21">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="AC22" s="21">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="AD22" s="21">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AE22" s="21">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="AF22" s="21">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="AG22" s="21">
+        <v>0.187</v>
+      </c>
+      <c r="AH22" s="21" t="s">
+        <v>842</v>
+      </c>
+      <c r="AI22" s="21" t="s">
+        <v>842</v>
+      </c>
+      <c r="AJ22" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="21">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="AL22" s="21">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" ht="20" customHeight="1">
+      <c r="A23" s="19">
+        <v>46046</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>843</v>
+      </c>
+      <c r="C23" s="22">
+        <v>2413</v>
+      </c>
+      <c r="D23" s="22">
+        <v>1925</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3.4027777777777775E-2</v>
+      </c>
+      <c r="F23" s="16">
+        <v>8</v>
+      </c>
+      <c r="G23" s="16">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="I23" s="21">
+        <v>0</v>
+      </c>
+      <c r="J23" s="21">
+        <v>0.02</v>
+      </c>
+      <c r="K23" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="L23" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="M23" s="21">
+        <v>0</v>
+      </c>
+      <c r="N23" s="21">
+        <v>0.193</v>
+      </c>
+      <c r="O23" s="21">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="P23" s="21">
+        <v>7.8E-2</v>
+      </c>
+      <c r="R23" s="21">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="T23" s="16">
+        <v>9</v>
+      </c>
+      <c r="U23" s="16">
+        <v>0</v>
+      </c>
+      <c r="W23" s="16">
         <v>38</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="X23" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="16">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="16">
         <v>2</v>
       </c>
-      <c r="R4" s="18" t="s">
-        <v>814</v>
-      </c>
-      <c r="S4" s="16">
-        <v>20</v>
-      </c>
-      <c r="T4" s="16">
-        <v>0</v>
-      </c>
-      <c r="U4" s="16">
+      <c r="AB23" s="21">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="AC23" s="21">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="AD23" s="21">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="21">
+        <v>0.247</v>
+      </c>
+      <c r="AF23" s="21">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="AG23" s="21">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="AH23" s="21">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="AI23" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="AJ23" s="21">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AK23" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL23" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" ht="20" customHeight="1">
+      <c r="A24" s="19">
+        <v>46043</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>844</v>
+      </c>
+      <c r="C24" s="22">
+        <v>3924</v>
+      </c>
+      <c r="D24" s="22">
+        <v>3164</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3.5416666666666666E-2</v>
+      </c>
+      <c r="F24" s="16">
+        <v>10</v>
+      </c>
+      <c r="G24" s="16">
+        <v>2</v>
+      </c>
+      <c r="H24" s="21">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="I24" s="21">
+        <v>0</v>
+      </c>
+      <c r="J24" s="21">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="K24" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="L24" s="21">
+        <v>0</v>
+      </c>
+      <c r="M24" s="21">
+        <v>0</v>
+      </c>
+      <c r="N24" s="21">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="O24" s="21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="P24" s="21">
+        <v>0.151</v>
+      </c>
+      <c r="R24" s="21">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="T24" s="16">
+        <v>38</v>
+      </c>
+      <c r="U24" s="16">
+        <v>2</v>
+      </c>
+      <c r="V24" s="16">
+        <v>2</v>
+      </c>
+      <c r="W24" s="16">
+        <v>41</v>
+      </c>
+      <c r="X24" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="16">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="16">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="21">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="AC24" s="21">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="AD24" s="21">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="AE24" s="21">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="AF24" s="21">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="AG24" s="21">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="AH24" s="21">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="AI24" s="21">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="AJ24" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL24" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" ht="20" customHeight="1">
+      <c r="A25" s="19">
+        <v>46041</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>845</v>
+      </c>
+      <c r="C25" s="22">
+        <v>7825</v>
+      </c>
+      <c r="D25" s="22">
+        <v>6654</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F25" s="16">
+        <v>13</v>
+      </c>
+      <c r="G25" s="16">
+        <v>1</v>
+      </c>
+      <c r="H25" s="21">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="I25" s="21">
+        <v>0</v>
+      </c>
+      <c r="J25" s="21">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="K25" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L25" s="21">
+        <v>0</v>
+      </c>
+      <c r="M25" s="21">
+        <v>0</v>
+      </c>
+      <c r="N25" s="21">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="O25" s="21">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="P25" s="21">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="R25" s="21">
+        <v>9.4E-2</v>
+      </c>
+      <c r="S25" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="T25" s="16">
+        <v>122</v>
+      </c>
+      <c r="U25" s="16">
+        <v>1</v>
+      </c>
+      <c r="V25" s="16">
         <v>3</v>
       </c>
-      <c r="V4" s="18" t="s">
-        <v>814</v>
-      </c>
-      <c r="W4" s="16">
-        <v>15</v>
-      </c>
-      <c r="X4" s="16">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="Y4" s="16">
-        <v>79.599999999999994</v>
-      </c>
-      <c r="Z4" s="16">
-        <v>5.6</v>
-      </c>
-      <c r="AA4" s="16">
-        <v>24.9</v>
-      </c>
-      <c r="AB4" s="16">
-        <v>30.1</v>
-      </c>
-      <c r="AC4" s="16">
-        <v>19.8</v>
-      </c>
-      <c r="AD4" s="16">
-        <v>13.7</v>
-      </c>
-      <c r="AE4" s="16">
+      <c r="W25" s="16">
+        <v>55</v>
+      </c>
+      <c r="X25" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="16">
+        <v>2</v>
+      </c>
+      <c r="AA25" s="16">
+        <v>19</v>
+      </c>
+      <c r="AB25" s="21">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="AC25" s="21">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="AD25" s="21">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="21">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="AF25" s="21">
+        <v>0.27</v>
+      </c>
+      <c r="AG25" s="21">
+        <v>0.19</v>
+      </c>
+      <c r="AH25" s="21">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="AI25" s="21">
+        <v>0.127</v>
+      </c>
+      <c r="AJ25" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL25" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" ht="20" customHeight="1">
+      <c r="A26" s="19">
+        <v>46039</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>846</v>
+      </c>
+      <c r="C26" s="22">
+        <v>7067</v>
+      </c>
+      <c r="D26" s="22">
+        <v>4219</v>
+      </c>
+      <c r="E26" s="18">
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="F26" s="16">
+        <v>6</v>
+      </c>
+      <c r="G26" s="16">
+        <v>2</v>
+      </c>
+      <c r="H26" s="21">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="I26" s="21">
+        <v>0</v>
+      </c>
+      <c r="J26" s="21">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="K26" s="21">
+        <v>0</v>
+      </c>
+      <c r="L26" s="21">
+        <v>0</v>
+      </c>
+      <c r="M26" s="21">
+        <v>0</v>
+      </c>
+      <c r="N26" s="21">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="O26" s="21">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="P26" s="21">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="R26" s="21">
+        <v>0.155</v>
+      </c>
+      <c r="T26" s="16">
+        <v>42</v>
+      </c>
+      <c r="U26" s="16">
+        <v>2</v>
+      </c>
+      <c r="W26" s="16">
+        <v>28</v>
+      </c>
+      <c r="X26" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="16">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="16">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="21">
+        <v>0.121</v>
+      </c>
+      <c r="AC26" s="21">
+        <v>0.879</v>
+      </c>
+      <c r="AD26" s="21">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="21">
+        <v>0.377</v>
+      </c>
+      <c r="AF26" s="21">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="AG26" s="21">
+        <v>0.189</v>
+      </c>
+      <c r="AH26" s="21">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="AI26" s="21">
+        <v>0.113</v>
+      </c>
+      <c r="AJ26" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL26" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" ht="20" customHeight="1">
+      <c r="A27" s="19">
+        <v>46035</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>847</v>
+      </c>
+      <c r="C27" s="22">
+        <v>4019</v>
+      </c>
+      <c r="D27" s="22">
+        <v>2338</v>
+      </c>
+      <c r="E27" s="18">
+        <v>2.7777777777777779E-3</v>
+      </c>
+      <c r="F27" s="16">
         <v>5</v>
       </c>
-      <c r="AF4" s="16">
-        <v>0.9</v>
-      </c>
-      <c r="AG4" s="16">
-        <v>97.3</v>
-      </c>
-      <c r="AH4" s="16">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="6" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="8" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="16" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="G27" s="16">
+        <v>1</v>
+      </c>
+      <c r="H27" s="21">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="I27" s="21">
+        <v>0</v>
+      </c>
+      <c r="J27" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="K27" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L27" s="21">
+        <v>0</v>
+      </c>
+      <c r="M27" s="21">
+        <v>0</v>
+      </c>
+      <c r="N27" s="21">
+        <v>0.252</v>
+      </c>
+      <c r="O27" s="21">
+        <v>0.312</v>
+      </c>
+      <c r="P27" s="21">
+        <v>0.127</v>
+      </c>
+      <c r="R27" s="21">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="S27" s="21">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="T27" s="16">
+        <v>28</v>
+      </c>
+      <c r="U27" s="16">
+        <v>1</v>
+      </c>
+      <c r="W27" s="16">
+        <v>38</v>
+      </c>
+      <c r="X27" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="16">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="16">
+        <v>4</v>
+      </c>
+      <c r="AB27" s="21">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="AC27" s="21">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="AD27" s="21">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="AE27" s="21">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="AF27" s="21">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="AG27" s="21">
+        <v>0.161</v>
+      </c>
+      <c r="AH27" s="21">
+        <v>6.3E-2</v>
+      </c>
+      <c r="AI27" s="21">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="AJ27" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" ht="20" customHeight="1">
+      <c r="A28" s="19">
+        <v>46031</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>848</v>
+      </c>
+      <c r="C28" s="22">
+        <v>11463</v>
+      </c>
+      <c r="D28" s="22">
+        <v>6451</v>
+      </c>
+      <c r="E28" s="18">
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="F28" s="16">
+        <v>7</v>
+      </c>
+      <c r="G28" s="16">
+        <v>3</v>
+      </c>
+      <c r="H28" s="21">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="I28" s="21">
+        <v>0</v>
+      </c>
+      <c r="J28" s="21">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="K28" s="21">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L28" s="21">
+        <v>0</v>
+      </c>
+      <c r="M28" s="21">
+        <v>0</v>
+      </c>
+      <c r="N28" s="21">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="O28" s="21">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="P28" s="21">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="R28" s="21">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="S28" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="T28" s="16">
+        <v>43</v>
+      </c>
+      <c r="U28" s="16">
+        <v>3</v>
+      </c>
+      <c r="W28" s="16">
+        <v>45</v>
+      </c>
+      <c r="X28" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="16">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="16">
+        <v>26</v>
+      </c>
+      <c r="AB28" s="21">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="AC28" s="21">
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="AD28" s="21">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AE28" s="21">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="AF28" s="21">
+        <v>0.155</v>
+      </c>
+      <c r="AG28" s="21">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="AH28" s="21">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="AI28" s="21">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="AJ28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL28" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" ht="20" customHeight="1">
+      <c r="A29" s="19">
+        <v>46016</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>849</v>
+      </c>
+      <c r="C29" s="22">
+        <v>1405595</v>
+      </c>
+      <c r="D29" s="22">
+        <v>690102</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="F29" s="16">
+        <v>9</v>
+      </c>
+      <c r="G29" s="16">
+        <v>323</v>
+      </c>
+      <c r="H29" s="21">
+        <v>0.495</v>
+      </c>
+      <c r="I29" s="21">
+        <v>0</v>
+      </c>
+      <c r="J29" s="21">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K29" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="L29" s="21">
+        <v>0</v>
+      </c>
+      <c r="M29" s="21">
+        <v>0</v>
+      </c>
+      <c r="N29" s="21">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="O29" s="21">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="P29" s="21">
+        <v>0.153</v>
+      </c>
+      <c r="R29" s="21">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="S29" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="T29" s="16">
+        <v>8431</v>
+      </c>
+      <c r="U29" s="16">
+        <v>323</v>
+      </c>
+      <c r="V29" s="16">
+        <v>40</v>
+      </c>
+      <c r="W29" s="16">
+        <v>2514</v>
+      </c>
+      <c r="X29" s="16">
+        <v>31</v>
+      </c>
+      <c r="Y29" s="16">
+        <v>61</v>
+      </c>
+      <c r="AA29" s="16">
+        <v>768</v>
+      </c>
+      <c r="AB29" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="AC29" s="21">
+        <v>0.998</v>
+      </c>
+      <c r="AD29" s="21">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AE29" s="21">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="AF29" s="21">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="AG29" s="21">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="AH29" s="21">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AI29" s="21">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AJ29" s="21">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AK29" s="21">
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="AL29" s="21">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" ht="20" customHeight="1">
+      <c r="A30" s="19">
+        <v>46010</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>850</v>
+      </c>
+      <c r="C30" s="22">
+        <v>122404</v>
+      </c>
+      <c r="D30" s="22">
+        <v>59435</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="F30" s="16">
+        <v>10</v>
+      </c>
+      <c r="G30" s="16">
+        <v>120</v>
+      </c>
+      <c r="H30" s="21">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="I30" s="21">
+        <v>0</v>
+      </c>
+      <c r="J30" s="21">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K30" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L30" s="21">
+        <v>0</v>
+      </c>
+      <c r="M30" s="21">
+        <v>0</v>
+      </c>
+      <c r="N30" s="21">
+        <v>0.625</v>
+      </c>
+      <c r="O30" s="21">
+        <v>3.1E-2</v>
+      </c>
+      <c r="P30" s="21">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="R30" s="21">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="S30" s="21">
+        <v>2.4E-2</v>
+      </c>
+      <c r="T30" s="16">
+        <v>1491</v>
+      </c>
+      <c r="U30" s="16">
+        <v>120</v>
+      </c>
+      <c r="V30" s="16">
+        <v>59</v>
+      </c>
+      <c r="W30" s="16">
+        <v>298</v>
+      </c>
+      <c r="X30" s="16">
+        <v>9</v>
+      </c>
+      <c r="Y30" s="16">
+        <v>10</v>
+      </c>
+      <c r="AA30" s="16">
+        <v>114</v>
+      </c>
+      <c r="AB30" s="21">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="AC30" s="21">
+        <v>0.98699999999999999</v>
+      </c>
+      <c r="AD30" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="AE30" s="21">
+        <v>0.182</v>
+      </c>
+      <c r="AF30" s="21">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="AG30" s="21">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="AH30" s="21">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="AI30" s="21">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="AJ30" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="AK30" s="21">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="AL30" s="21">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" ht="20" customHeight="1">
+      <c r="A31" s="19">
+        <v>46007</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>851</v>
+      </c>
+      <c r="C31" s="22">
+        <v>3646</v>
+      </c>
+      <c r="D31" s="22">
+        <v>3076</v>
+      </c>
+      <c r="E31" s="18">
+        <v>4.0972222222222222E-2</v>
+      </c>
+      <c r="F31" s="16">
+        <v>9</v>
+      </c>
+      <c r="G31" s="16">
+        <v>4</v>
+      </c>
+      <c r="H31" s="21">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="I31" s="21">
+        <v>0</v>
+      </c>
+      <c r="J31" s="21">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K31" s="21">
+        <v>0</v>
+      </c>
+      <c r="L31" s="21">
+        <v>0</v>
+      </c>
+      <c r="M31" s="21">
+        <v>0</v>
+      </c>
+      <c r="N31" s="21">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="O31" s="21">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="P31" s="21">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="Q31" s="21">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="R31" s="21">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="T31" s="16">
+        <v>29</v>
+      </c>
+      <c r="U31" s="16">
+        <v>4</v>
+      </c>
+      <c r="V31" s="16">
+        <v>1</v>
+      </c>
+      <c r="W31" s="16">
+        <v>18</v>
+      </c>
+      <c r="X31" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="16">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="16">
+        <v>1</v>
+      </c>
+      <c r="AB31" s="21">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="AC31" s="21">
+        <v>8.06</v>
+      </c>
+      <c r="AD31" s="21">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AE31" s="21">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="AF31" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="AG31" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="AH31" s="21">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="AI31" s="21">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="21">
+        <v>1</v>
+      </c>
+      <c r="AL31" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" ht="20" customHeight="1">
+      <c r="A32" s="19">
+        <v>45999</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>852</v>
+      </c>
+      <c r="C32" s="22">
+        <v>4134</v>
+      </c>
+      <c r="D32" s="22">
+        <v>3314</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3.8194444444444448E-2</v>
+      </c>
+      <c r="F32" s="16">
+        <v>11</v>
+      </c>
+      <c r="G32" s="16">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="X1:AH1"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="P1:W1"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="AB1:AL1"/>
+    <mergeCell ref="B1:M1"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>